--- a/final_data_pipeline/output/325180longform_elec_options_nowhp.xlsx
+++ b/final_data_pipeline/output/325180longform_elec_options_nowhp.xlsx
@@ -1147,7 +1147,7 @@
         <v>97</v>
       </c>
       <c r="I10">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="J10">
         <v>8000</v>
@@ -1162,10 +1162,10 @@
         <v>43040.19259695899</v>
       </c>
       <c r="N10">
-        <v>0.9405645161290322</v>
+        <v>0.9516859959956178</v>
       </c>
       <c r="O10">
-        <v>0.9635833333333333</v>
+        <v>0.9753614246104579</v>
       </c>
       <c r="P10">
         <v>5.380024074619874</v>
@@ -1200,7 +1200,7 @@
         <v>98</v>
       </c>
       <c r="I11">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="J11">
         <v>8000</v>
@@ -1647,7 +1647,7 @@
         <v>97</v>
       </c>
       <c r="I20">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="J20">
         <v>8000</v>
@@ -1662,10 +1662,10 @@
         <v>35888.00851422216</v>
       </c>
       <c r="N20">
-        <v>0.9405645161290322</v>
+        <v>0.9495669873270495</v>
       </c>
       <c r="O20">
-        <v>0.9635833333333333</v>
+        <v>0.9731165936130245</v>
       </c>
       <c r="P20">
         <v>4.48600106427777</v>
@@ -1700,7 +1700,7 @@
         <v>98</v>
       </c>
       <c r="I21">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="J21">
         <v>8000</v>
@@ -1847,7 +1847,7 @@
         <v>97</v>
       </c>
       <c r="I24">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="J24">
         <v>8000</v>
@@ -1862,10 +1862,10 @@
         <v>271528.9521856017</v>
       </c>
       <c r="N24">
-        <v>0.9405645161290322</v>
+        <v>0.9511946531936644</v>
       </c>
       <c r="O24">
-        <v>0.9635833333333333</v>
+        <v>0.9748408768576692</v>
       </c>
       <c r="P24">
         <v>33.94111902320021</v>
@@ -1900,7 +1900,7 @@
         <v>98</v>
       </c>
       <c r="I25">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="J25">
         <v>8000</v>
@@ -1947,7 +1947,7 @@
         <v>97</v>
       </c>
       <c r="I26">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="J26">
         <v>8000</v>
@@ -1962,10 +1962,10 @@
         <v>115580.0317946794</v>
       </c>
       <c r="N26">
-        <v>0.9405645161290322</v>
+        <v>0.9583158770332573</v>
       </c>
       <c r="O26">
-        <v>0.9635833333333333</v>
+        <v>0.9823871532785465</v>
       </c>
       <c r="P26">
         <v>14.44750397433493</v>
@@ -2000,7 +2000,7 @@
         <v>98</v>
       </c>
       <c r="I27">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="J27">
         <v>8000</v>
@@ -2347,7 +2347,7 @@
         <v>97</v>
       </c>
       <c r="I34">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="J34">
         <v>8000</v>
@@ -2362,10 +2362,10 @@
         <v>85232.79659721626</v>
       </c>
       <c r="N34">
-        <v>0.9405645161290322</v>
+        <v>0.9712571710566898</v>
       </c>
       <c r="O34">
-        <v>0.9635833333333333</v>
+        <v>0.9961106502456767</v>
       </c>
       <c r="P34">
         <v>10.65409957465203</v>
@@ -2400,7 +2400,7 @@
         <v>98</v>
       </c>
       <c r="I35">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="J35">
         <v>8000</v>
@@ -2647,7 +2647,7 @@
         <v>97</v>
       </c>
       <c r="I40">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="J40">
         <v>8000</v>
@@ -2662,10 +2662,10 @@
         <v>102483.8971167525</v>
       </c>
       <c r="N40">
-        <v>0.9405645161290322</v>
+        <v>0.9741566255742371</v>
       </c>
       <c r="O40">
-        <v>0.9635833333333333</v>
+        <v>0.9991870829399434</v>
       </c>
       <c r="P40">
         <v>12.81048713959406</v>
@@ -2700,7 +2700,7 @@
         <v>98</v>
       </c>
       <c r="I41">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="J41">
         <v>8000</v>
@@ -3047,7 +3047,7 @@
         <v>97</v>
       </c>
       <c r="I48">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="J48">
         <v>8000</v>
@@ -3062,10 +3062,10 @@
         <v>24327.06538088986</v>
       </c>
       <c r="N48">
-        <v>0.9405645161290322</v>
+        <v>0.9760891465058971</v>
       </c>
       <c r="O48">
-        <v>0.9635833333333333</v>
+        <v>1.001237913506406</v>
       </c>
       <c r="P48">
         <v>3.040883172611232</v>
@@ -3100,7 +3100,7 @@
         <v>98</v>
       </c>
       <c r="I49">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="J49">
         <v>8000</v>
@@ -3147,7 +3147,7 @@
         <v>97</v>
       </c>
       <c r="I50">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="J50">
         <v>8000</v>
@@ -3162,10 +3162,10 @@
         <v>29414.88774109125</v>
       </c>
       <c r="N50">
-        <v>0.9405645161290322</v>
+        <v>0.970793063583815</v>
       </c>
       <c r="O50">
-        <v>0.9635833333333333</v>
+        <v>0.995618273140397</v>
       </c>
       <c r="P50">
         <v>3.676860967636406</v>
@@ -3200,7 +3200,7 @@
         <v>98</v>
       </c>
       <c r="I51">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="J51">
         <v>8000</v>
@@ -3247,7 +3247,7 @@
         <v>97</v>
       </c>
       <c r="I52">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="J52">
         <v>8000</v>
@@ -3262,10 +3262,10 @@
         <v>63857.5285003954</v>
       </c>
       <c r="N52">
-        <v>0.9405645161290322</v>
+        <v>0.9760891465058971</v>
       </c>
       <c r="O52">
-        <v>0.9635833333333333</v>
+        <v>1.001237913506406</v>
       </c>
       <c r="P52">
         <v>7.982191062549425</v>
@@ -3300,7 +3300,7 @@
         <v>98</v>
       </c>
       <c r="I53">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="J53">
         <v>8000</v>
@@ -3447,7 +3447,7 @@
         <v>98</v>
       </c>
       <c r="I56">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="J56">
         <v>8000</v>
@@ -3894,7 +3894,7 @@
         <v>97</v>
       </c>
       <c r="I65">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="J65">
         <v>8000</v>
@@ -3909,10 +3909,10 @@
         <v>61543.33164717858</v>
       </c>
       <c r="N65">
-        <v>0.9405645161290322</v>
+        <v>0.9516859959956178</v>
       </c>
       <c r="O65">
-        <v>0.9635833333333333</v>
+        <v>0.9753614246104579</v>
       </c>
       <c r="P65">
         <v>7.692916455897323</v>
@@ -3947,7 +3947,7 @@
         <v>98</v>
       </c>
       <c r="I66">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="J66">
         <v>8000</v>
@@ -4094,7 +4094,7 @@
         <v>97</v>
       </c>
       <c r="I69">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="J69">
         <v>8000</v>
@@ -4109,10 +4109,10 @@
         <v>138506.4124765754</v>
       </c>
       <c r="N69">
-        <v>0.9405645161290322</v>
+        <v>0.9712571710566898</v>
       </c>
       <c r="O69">
-        <v>0.9635833333333333</v>
+        <v>0.9961106502456767</v>
       </c>
       <c r="P69">
         <v>17.31330155957192</v>
@@ -4147,7 +4147,7 @@
         <v>98</v>
       </c>
       <c r="I70">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="J70">
         <v>8000</v>
@@ -4194,7 +4194,7 @@
         <v>97</v>
       </c>
       <c r="I71">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="J71">
         <v>8000</v>
@@ -4209,10 +4209,10 @@
         <v>4608.65326029847</v>
       </c>
       <c r="N71">
-        <v>0.9405645161290322</v>
+        <v>0.9521050214763401</v>
       </c>
       <c r="O71">
-        <v>0.9635833333333333</v>
+        <v>0.9758053708974481</v>
       </c>
       <c r="P71">
         <v>0.5760816575373088</v>
@@ -4247,7 +4247,7 @@
         <v>98</v>
       </c>
       <c r="I72">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="J72">
         <v>8000</v>
@@ -4294,7 +4294,7 @@
         <v>97</v>
       </c>
       <c r="I73">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="J73">
         <v>8000</v>
@@ -4309,10 +4309,10 @@
         <v>254359.3016213042</v>
       </c>
       <c r="N73">
-        <v>0.9405645161290322</v>
+        <v>0.9696645907267841</v>
       </c>
       <c r="O73">
-        <v>0.9635833333333333</v>
+        <v>0.9944211305850406</v>
       </c>
       <c r="P73">
         <v>31.79491270266302</v>
@@ -4347,7 +4347,7 @@
         <v>98</v>
       </c>
       <c r="I74">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="J74">
         <v>8000</v>
@@ -4394,7 +4394,7 @@
         <v>97</v>
       </c>
       <c r="I75">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="J75">
         <v>8000</v>
@@ -4409,10 +4409,10 @@
         <v>279333.6001559282</v>
       </c>
       <c r="N75">
-        <v>0.9405645161290322</v>
+        <v>0.9497676359185355</v>
       </c>
       <c r="O75">
-        <v>0.9635833333333333</v>
+        <v>0.9733291418446532</v>
       </c>
       <c r="P75">
         <v>34.91670001949102</v>
@@ -4447,7 +4447,7 @@
         <v>98</v>
       </c>
       <c r="I76">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="J76">
         <v>8000</v>
@@ -4541,7 +4541,7 @@
         <v>97</v>
       </c>
       <c r="I78">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="J78">
         <v>8000</v>
@@ -4556,10 +4556,10 @@
         <v>33942.23259680699</v>
       </c>
       <c r="N78">
-        <v>0.9405645161290322</v>
+        <v>0.9516859959956178</v>
       </c>
       <c r="O78">
-        <v>0.9635833333333333</v>
+        <v>0.9753614246104579</v>
       </c>
       <c r="P78">
         <v>4.242779074600874</v>
@@ -4594,7 +4594,7 @@
         <v>98</v>
       </c>
       <c r="I79">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="J79">
         <v>8000</v>
@@ -4641,7 +4641,7 @@
         <v>97</v>
       </c>
       <c r="I80">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="J80">
         <v>8000</v>
@@ -4656,10 +4656,10 @@
         <v>83154.29555197115</v>
       </c>
       <c r="N80">
-        <v>0.9405645161290322</v>
+        <v>0.9163022129108289</v>
       </c>
       <c r="O80">
-        <v>0.9635833333333333</v>
+        <v>0.9379207786940652</v>
       </c>
       <c r="P80">
         <v>10.39428694399639</v>
@@ -4694,7 +4694,7 @@
         <v>98</v>
       </c>
       <c r="I81">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="J81">
         <v>8000</v>
@@ -5041,7 +5041,7 @@
         <v>97</v>
       </c>
       <c r="I88">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="J88">
         <v>8000</v>
@@ -5056,10 +5056,10 @@
         <v>2915.399335321758</v>
       </c>
       <c r="N88">
-        <v>0.9405645161290322</v>
+        <v>0.9516859959956178</v>
       </c>
       <c r="O88">
-        <v>0.9635833333333333</v>
+        <v>0.9753614246104579</v>
       </c>
       <c r="P88">
         <v>0.3644249169152198</v>
@@ -5094,7 +5094,7 @@
         <v>98</v>
       </c>
       <c r="I89">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="J89">
         <v>8000</v>
@@ -5141,7 +5141,7 @@
         <v>97</v>
       </c>
       <c r="I90">
-        <v>10</v>
+        <v>5.486111111111112</v>
       </c>
       <c r="J90">
         <v>8000</v>
@@ -5156,10 +5156,10 @@
         <v>84591.37819971226</v>
       </c>
       <c r="N90">
-        <v>0.9405645161290322</v>
+        <v>0.9270655773901523</v>
       </c>
       <c r="O90">
-        <v>0.9635833333333333</v>
+        <v>0.9492998859749143</v>
       </c>
       <c r="P90">
         <v>10.57392227496403</v>
@@ -5194,7 +5194,7 @@
         <v>98</v>
       </c>
       <c r="I91">
-        <v>10</v>
+        <v>5.486111111111112</v>
       </c>
       <c r="J91">
         <v>8000</v>
@@ -5241,7 +5241,7 @@
         <v>97</v>
       </c>
       <c r="I92">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="J92">
         <v>8000</v>
@@ -5256,10 +5256,10 @@
         <v>121046.5544900213</v>
       </c>
       <c r="N92">
-        <v>0.9405645161290322</v>
+        <v>0.9166889846297158</v>
       </c>
       <c r="O92">
-        <v>0.9635833333333333</v>
+        <v>0.9383295263284442</v>
       </c>
       <c r="P92">
         <v>15.13081931125267</v>
@@ -5294,7 +5294,7 @@
         <v>98</v>
       </c>
       <c r="I93">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="J93">
         <v>8000</v>
@@ -5741,7 +5741,7 @@
         <v>97</v>
       </c>
       <c r="I102">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="J102">
         <v>8000</v>
@@ -5756,10 +5756,10 @@
         <v>64794.45751674948</v>
       </c>
       <c r="N102">
-        <v>0.9405645161290322</v>
+        <v>0.9521050214763401</v>
       </c>
       <c r="O102">
-        <v>0.9635833333333333</v>
+        <v>0.9758053708974481</v>
       </c>
       <c r="P102">
         <v>8.099307189593684</v>
@@ -5794,7 +5794,7 @@
         <v>98</v>
       </c>
       <c r="I103">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="J103">
         <v>8000</v>
@@ -5841,7 +5841,7 @@
         <v>97</v>
       </c>
       <c r="I104">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="J104">
         <v>8000</v>
@@ -5856,10 +5856,10 @@
         <v>96305.66348079426</v>
       </c>
       <c r="N104">
-        <v>0.9405645161290322</v>
+        <v>0.9516859959956178</v>
       </c>
       <c r="O104">
-        <v>0.9635833333333333</v>
+        <v>0.9753614246104579</v>
       </c>
       <c r="P104">
         <v>12.03820793509928</v>
@@ -5894,7 +5894,7 @@
         <v>98</v>
       </c>
       <c r="I105">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="J105">
         <v>8000</v>
@@ -6141,7 +6141,7 @@
         <v>97</v>
       </c>
       <c r="I110">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="J110">
         <v>8000</v>
@@ -6156,10 +6156,10 @@
         <v>54500.96489236086</v>
       </c>
       <c r="N110">
-        <v>0.9405645161290322</v>
+        <v>0.9163022129108289</v>
       </c>
       <c r="O110">
-        <v>0.9635833333333333</v>
+        <v>0.9379207786940652</v>
       </c>
       <c r="P110">
         <v>6.812620611545108</v>
@@ -6194,7 +6194,7 @@
         <v>98</v>
       </c>
       <c r="I111">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="J111">
         <v>8000</v>
@@ -6241,7 +6241,7 @@
         <v>97</v>
       </c>
       <c r="I112">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="J112">
         <v>8000</v>
@@ -6256,10 +6256,10 @@
         <v>57082.41941120433</v>
       </c>
       <c r="N112">
-        <v>0.9405645161290322</v>
+        <v>0.9758169225763468</v>
       </c>
       <c r="O112">
-        <v>0.9635833333333333</v>
+        <v>1.000949006909155</v>
       </c>
       <c r="P112">
         <v>7.135302426400542</v>
@@ -6294,7 +6294,7 @@
         <v>98</v>
       </c>
       <c r="I113">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="J113">
         <v>8000</v>
